--- a/artfynd/A 13897-2026 artfynd.xlsx
+++ b/artfynd/A 13897-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93249709</v>
+        <v>89354781</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenmur vid fornåker, håligheter och bon, Gstr</t>
+          <t>Håla ner under mark, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599170.0305904553</v>
+        <v>599141</v>
       </c>
       <c r="R2" t="n">
-        <v>6725562.170429336</v>
+        <v>6725525</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Troligtvis bor det ett gäng i håligheterna i de gamla stenmurarna i fornåkern Hästhagvreten, ser dem ofta strosa omkring obekymrat på stigarna och i trollskogen här.</t>
+          <t>Bajs utanför ihåligt träd, gångar ner, bo?</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,59 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110692523</v>
+        <v>89354869</v>
       </c>
       <c r="B3" t="n">
-        <v>96266</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>100053</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skuggig fornåker precis innanför EU skyddad öppen åkermark, Gstr</t>
+          <t>Fornlämning, Biotop Stenmur, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599342.7087169121</v>
+        <v>599308</v>
       </c>
       <c r="R3" t="n">
-        <v>6725590.490257024</v>
+        <v>6725602</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,27 +858,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-12-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inte säker på vilken sort här, men dessa gömmer sig på sina ställen bredvid liljekonvaljer bla</t>
+          <t>Igelkottbajs efter kanten på en annan fornlämning. (Fossil Åkermark) Många sådana platser i området där Igelkottar bor. Svårt att lokalisa vilka hål i alla murarna då man ej får röra...</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -927,57 +895,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110692807</v>
+        <v>93249709</v>
       </c>
       <c r="B4" t="n">
-        <v>96266</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>100053</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fornåker, miljö bredvid MTB och skidspår, Gstr</t>
+          <t>Stenmur vid fornåker, håligheter och bon, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599240.2022055004</v>
+        <v>599171</v>
       </c>
       <c r="R4" t="n">
-        <v>6725619.054789642</v>
+        <v>6725562</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,22 +968,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Troligtvis bor det ett gäng i håligheterna i de gamla stenmurarna i fornåkern Hästhagvreten, ser dem ofta strosa omkring obekymrat på stigarna och i trollskogen här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,6 +1002,857 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>93249852</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56845</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenmur Fornåker, bon?, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>599278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6725539</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89373713</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kanten av åkern, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>599162</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6725481</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-12-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-12-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110693781</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strandskyddad bäck, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>599431</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6725602</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88990395</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åkerkant, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>599342</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6725556</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-05-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-05-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>92366444</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bredvid Stigen, Naturvärdesområde, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>599121</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6725581</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Otroligt fint med alla Blåsippor runt stigarna och backarna i detta friluftsområde nu. Många naturvärdesträd i bakgrunden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110692523</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skuggig fornåker precis innanför EU skyddad öppen åkermark, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>599342</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6725590</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Inte säker på vilken sort här, men dessa gömmer sig på sina ställen bredvid liljekonvaljer bla</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110692636</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fornåker, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>599359</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6725602</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>osäker vilken mer specifik</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110692807</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fornåker, miljö bredvid MTB och skidspår, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>599240</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6725620</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>fredrik wallström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13897-2026 artfynd.xlsx
+++ b/artfynd/A 13897-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89354781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89354869</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93249709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93249852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89373713</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110693781</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88990395</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92366444</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110692523</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110692636</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,8 +1908,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110692807</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>